--- a/感度分析.xlsx
+++ b/感度分析.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\ドキュメント\making_article\論文\生成AIによる自治体事務支援が職員の疲弊構造に与える影響\major revision\修正１\修正３（未送付20260524)\［予定］送付ファイル\コード及び感度分析表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C967D1FA-DCA5-4E50-A02A-A367CE1B00C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8860617-C47B-4C30-8199-38C4708FD50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5655" yWindow="1530" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-31185" yWindow="3225" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="感度分析結果" sheetId="1" r:id="rId1"/>
@@ -329,9 +329,6 @@
     <t>【θの定義】AI支援なし繁忙期P90の中央値（MC=1000）。</t>
   </si>
   <si>
-    <t>【モデル設定】T=52週, 繁忙期=第13〜31週, N=500, MC=1000（θのみMC=1000）。NOISE_F=5.0, F0=clip(N(50,10))。乱数シードSEED=42。</t>
-  </si>
-  <si>
     <t>【λの対象】本感度分析は標準群（λ∈U(0.02,0.08)）のみを対象とする。</t>
   </si>
   <si>
@@ -343,7 +340,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>【安定性クリップ】</t>
+      <t>【モデル設定】</t>
     </r>
     <r>
       <rPr>
@@ -352,7 +349,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>λ</t>
+      <t>T=52</t>
     </r>
     <r>
       <rPr>
@@ -362,7 +359,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>は、変動後も</t>
+      <t>週</t>
     </r>
     <r>
       <rPr>
@@ -371,7 +368,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>ρ+βλ&lt;0.95</t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -381,7 +378,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>を満たすようクリップしている。また、</t>
+      <t>繁忙期</t>
     </r>
     <r>
       <rPr>
@@ -390,7 +387,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>ρ</t>
+      <t>=</t>
     </r>
     <r>
       <rPr>
@@ -400,7 +397,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>の変動範囲自体も、数値的安定性のため上限を</t>
+      <t>第</t>
     </r>
     <r>
       <rPr>
@@ -409,7 +406,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>0.95</t>
+      <t>13</t>
     </r>
     <r>
       <rPr>
@@ -419,7 +416,405 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>に制限している。</t>
+      <t>〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>週</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, N=500, MC=1000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>θ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>のみ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MC=1000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOISE_F=5.0, F0=clip(N(50,10))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。乱数シード</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SEED=42</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>【安定性クリップ】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>λ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は、変動後も</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ρ+βλ&lt;0.95</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を満たすようクリップしている。また、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ρ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の変動範囲自体も、数値的安定性のため上限を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.99</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>とし、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>ρ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>＞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.95</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の標本では</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>λ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>とした。このため、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>ρ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>％条件では実質持ち越し率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Λ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.95</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を超える場合があるが、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Λ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>＜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF444444"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は維持される。</t>
     </r>
     <phoneticPr fontId="12"/>
   </si>
@@ -428,7 +823,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -528,6 +923,20 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF444444"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF444444"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -736,20 +1145,20 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1054,7 +1463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1068,7 +1477,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="42"/>
@@ -1082,7 +1491,7 @@
       <c r="J1" s="42"/>
     </row>
     <row r="2" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="42"/>
@@ -1096,7 +1505,7 @@
       <c r="J2" s="42"/>
     </row>
     <row r="3" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="43" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="42"/>
@@ -1480,7 +1889,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="29"/>
       <c r="B17" s="33" t="s">
         <v>31</v>
@@ -1510,7 +1919,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="34" t="s">
         <v>71</v>
       </c>
@@ -1542,7 +1951,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="36"/>
       <c r="B19" s="7" t="s">
         <v>23</v>
@@ -1572,7 +1981,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="36"/>
       <c r="B20" s="40" t="s">
         <v>31</v>
@@ -1602,8 +2011,8 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="44" t="s">
+    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="46" t="s">
         <v>80</v>
       </c>
       <c r="B22" s="42"/>
@@ -1616,8 +2025,8 @@
       <c r="I22" s="42"/>
       <c r="J22" s="42"/>
     </row>
-    <row r="23" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="43" t="s">
+    <row r="23" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="41" t="s">
         <v>81</v>
       </c>
       <c r="B23" s="42"/>
@@ -1630,8 +2039,8 @@
       <c r="I23" s="42"/>
       <c r="J23" s="42"/>
     </row>
-    <row r="24" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="43" t="s">
+    <row r="24" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="41" t="s">
         <v>82</v>
       </c>
       <c r="B24" s="42"/>
@@ -1644,22 +2053,25 @@
       <c r="I24" s="42"/>
       <c r="J24" s="42"/>
     </row>
-    <row r="25" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="46" t="s">
+    <row r="25" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="42"/>
-    </row>
-    <row r="26" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="43" t="s">
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
+      <c r="L25" s="44"/>
+      <c r="M25" s="44"/>
+    </row>
+    <row r="26" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="41" t="s">
         <v>83</v>
       </c>
       <c r="B26" s="42"/>
@@ -1672,9 +2084,9 @@
       <c r="I26" s="42"/>
       <c r="J26" s="42"/>
     </row>
-    <row r="27" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="43" t="s">
-        <v>84</v>
+    <row r="27" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="44" t="s">
+        <v>85</v>
       </c>
       <c r="B27" s="42"/>
       <c r="C27" s="42"/>
@@ -1686,9 +2098,9 @@
       <c r="I27" s="42"/>
       <c r="J27" s="42"/>
     </row>
-    <row r="28" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="43" t="s">
-        <v>85</v>
+    <row r="28" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="41" t="s">
+        <v>84</v>
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="42"/>
@@ -1702,16 +2114,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A25:J25"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A27:J27"/>
     <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A25:M25"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <phoneticPr fontId="12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
